--- a/exports/7186_palmapampa.xlsx
+++ b/exports/7186_palmapampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7412,22 +7412,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>61240357</t>
+          <t>61739792</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HUAMANCHAQUI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TERRY JHON</t>
+          <t>JEANPIER DIEGO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7436,21 +7436,21 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>25/06/2005</t>
+          <t>16/09/2009</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>09/03/2015</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>61739792</t>
+          <t>81479831</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>JEANPIER DIEGO</t>
+          <t>CRISTIAM ALEXIS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7499,21 +7499,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>16/09/2009</t>
+          <t>10/06/2015</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>09/03/2015</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>81479831</t>
+          <t>45854743</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HUANCAS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CRISTIAM ALEXIS</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7562,21 +7562,21 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10/06/2015</t>
+          <t>02/01/1978</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>10/04/2018</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7601,22 +7601,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>45854743</t>
+          <t>46891699</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SOBRADO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HUANCAS</t>
+          <t>MARCHINO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>AHOLIAB ZACARIAS</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7625,11 +7625,11 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>02/01/1978</t>
+          <t>02/11/1990</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>10/04/2018</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7664,22 +7664,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>46891699</t>
+          <t>20997966</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SOBRADO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MARCHINO</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AHOLIAB ZACARIAS</t>
+          <t>WALTER EDMUNDO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7688,21 +7688,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>02/11/1990</t>
+          <t>09/11/1966</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7727,40 +7727,40 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20997966</t>
+          <t>81391391</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>CAVIÑO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>WALTER EDMUNDO</t>
+          <t>AKEMY DAYZUQUI</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>09/11/1966</t>
+          <t>04/01/2002</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7790,22 +7790,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>81391391</t>
+          <t>77242280</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CAVIÑO</t>
+          <t>POVIS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AKEMY DAYZUQUI</t>
+          <t>ERIKA MARLENI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7814,16 +7814,16 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>04/01/2002</t>
+          <t>17/02/1995</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>19/09/2013</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7853,22 +7853,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>77242280</t>
+          <t>61282617</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>POVIS</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ERIKA MARLENI</t>
+          <t>YIN SUE SHIRLEY</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7877,21 +7877,21 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>17/02/1995</t>
+          <t>04/02/2008</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>19/09/2013</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7916,7 +7916,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>61282617</t>
+          <t>20968626</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>YIN SUE SHIRLEY</t>
+          <t>REGINA LUISA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>04/02/2008</t>
+          <t>07/09/1957</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7979,22 +7979,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>41223863</t>
+          <t>42978891</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>URETA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>COOPER PERCY</t>
+          <t>ROY MIRKO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>19/02/1982</t>
+          <t>10/10/1984</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8042,40 +8042,40 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20968626</t>
+          <t>81411696</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>REGINA LUISA</t>
+          <t>JHONN ALEXIS</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>07/09/1957</t>
+          <t>15/11/2014</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8105,40 +8105,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>42978891</t>
+          <t>73668035</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>URETA</t>
+          <t>VILCHEZ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MUNIVE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ROY MIRKO</t>
+          <t>LUCY JHANET</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>10/10/1984</t>
+          <t>21/03/1998</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8162,132 +8162,6 @@
         </is>
       </c>
       <c r="M123" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>81411696</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>VELIZ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>HINOSTROZA</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>JHONN ALEXIS</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>12</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>15/11/2014</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>2.ADOLESCENTE</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>15/05/2025</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M124" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>73668035</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>VILCHEZ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>MUNIVE</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LUCY JHANET</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>28</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>21/03/1998</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>05/04/2025</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
         <v>120602</v>
       </c>
     </row>

--- a/exports/7186_palmapampa.xlsx
+++ b/exports/7186_palmapampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7412,22 +7412,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>61739792</t>
+          <t>61240357</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HUAMANCHAQUI</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>JEANPIER DIEGO</t>
+          <t>TERRY JHON</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7436,21 +7436,21 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>16/09/2009</t>
+          <t>25/06/2005</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>09/03/2015</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>81479831</t>
+          <t>61739792</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CRISTIAM ALEXIS</t>
+          <t>JEANPIER DIEGO</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7499,21 +7499,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>10/06/2015</t>
+          <t>16/09/2009</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>09/03/2015</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>45854743</t>
+          <t>81479831</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HUANCAS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>CRISTIAM ALEXIS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7562,21 +7562,21 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>02/01/1978</t>
+          <t>10/06/2015</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>10/04/2018</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7601,22 +7601,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>46891699</t>
+          <t>45854743</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SOBRADO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MARCHINO</t>
+          <t>HUANCAS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AHOLIAB ZACARIAS</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7625,11 +7625,11 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>02/11/1990</t>
+          <t>02/01/1978</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>10/04/2018</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7664,22 +7664,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>20997966</t>
+          <t>46891699</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SOBRADO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>MARCHINO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>WALTER EDMUNDO</t>
+          <t>AHOLIAB ZACARIAS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7688,21 +7688,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>09/11/1966</t>
+          <t>02/11/1990</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7727,40 +7727,40 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>81391391</t>
+          <t>20997966</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CAVIÑO</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AKEMY DAYZUQUI</t>
+          <t>WALTER EDMUNDO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>04/01/2002</t>
+          <t>09/11/1966</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7790,22 +7790,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>77242280</t>
+          <t>81391391</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>POVIS</t>
+          <t>CAVIÑO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ERIKA MARLENI</t>
+          <t>AKEMY DAYZUQUI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7814,16 +7814,16 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>17/02/1995</t>
+          <t>04/01/2002</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>19/09/2013</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7853,22 +7853,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>61282617</t>
+          <t>77242280</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>POVIS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>YIN SUE SHIRLEY</t>
+          <t>ERIKA MARLENI</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7877,21 +7877,21 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>04/02/2008</t>
+          <t>17/02/1995</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/09/2013</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7916,7 +7916,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20968626</t>
+          <t>61282617</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>REGINA LUISA</t>
+          <t>YIN SUE SHIRLEY</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>07/09/1957</t>
+          <t>04/02/2008</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7979,22 +7979,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>42978891</t>
+          <t>41223863</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>URETA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ROY MIRKO</t>
+          <t>COOPER PERCY</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>10/10/1984</t>
+          <t>19/02/1982</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8042,40 +8042,40 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>81411696</t>
+          <t>20968626</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>JHONN ALEXIS</t>
+          <t>REGINA LUISA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>15/11/2014</t>
+          <t>07/09/1957</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8105,63 +8105,189 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>42978891</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>URETA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ROY MIRKO</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>42</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>10/10/1984</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>06/03/2024</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>81411696</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>VELIZ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>HINOSTROZA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>JHONN ALEXIS</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>12</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>15/11/2014</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2.ADOLESCENTE</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>15/05/2025</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>73668035</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>VILCHEZ</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>MUNIVE</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>LUCY JHANET</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F123" t="n">
+      <c r="F125" t="n">
         <v>28</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>21/03/1998</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>3.JOVEN</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>05/04/2025</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M123" t="n">
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
         <v>120602</v>
       </c>
     </row>

--- a/exports/7186_palmapampa.xlsx
+++ b/exports/7186_palmapampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>75545372</t>
+          <t>40154849</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1882,35 +1882,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FRANKLIN RENE</t>
+          <t>ESTHER GUMERCINDA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14/08/1999</t>
+          <t>21/02/1979</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NRUS - CONVENIO SUNAT-SIS, LEY N°29951 Y D.S. N°106-2013-EF</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40154849</t>
+          <t>41566570</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1950,20 +1950,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ESTHER GUMERCINDA</t>
+          <t>MOISES ELIAS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21/02/1979</t>
+          <t>19/09/1980</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>10/09/2012</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41566570</t>
+          <t>41976771</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2013,20 +2013,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MOISES ELIAS</t>
+          <t>MARIZOL MARINA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19/09/1980</t>
+          <t>12/05/1982</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>10/09/2012</t>
+          <t>30/05/2018</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>41976771</t>
+          <t>73667972</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,30 +2076,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MARIZOL MARINA</t>
+          <t>GIAN CARLOS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12/05/1982</t>
+          <t>16/12/2002</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30/05/2018</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,22 +2124,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>73667972</t>
+          <t>90660467</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>ECHEVARRIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>QUICHCA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GIAN CARLOS</t>
+          <t>ABEL YEICO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2148,16 +2148,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16/12/2002</t>
+          <t>03/03/2018</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,40 +2187,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>90660467</t>
+          <t>60010710</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ECHEVARRIA</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>QUICHCA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ABEL YEICO</t>
+          <t>NATALY YESENIA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>03/03/2018</t>
+          <t>02/12/1996</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,22 +2250,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>60010710</t>
+          <t>73664445</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NATALY YESENIA</t>
+          <t>LISBETH GUISELA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>02/12/1996</t>
+          <t>08/07/1999</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>73664445</t>
+          <t>73660242</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LISBETH GUISELA</t>
+          <t>LUZMILA SHEILA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>08/07/1999</t>
+          <t>13/11/2000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2376,7 +2376,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>73660242</t>
+          <t>63410555</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LUZMILA SHEILA</t>
+          <t>LUZ MELIZA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>13/11/2000</t>
+          <t>05/07/2011</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>05/12/2011</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>63410555</t>
+          <t>90688461</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2454,25 +2454,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LUZ MELIZA</t>
+          <t>JESUS YODIEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>05/07/2011</t>
+          <t>21/03/2018</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>05/12/2011</t>
+          <t>21/03/2023</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>90688461</t>
+          <t>43847576</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JESUS YODIEL</t>
+          <t>ANGEL RAUL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2526,16 +2526,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21/03/2018</t>
+          <t>02/10/1986</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21/03/2023</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43847576</t>
+          <t>47618809</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2580,20 +2580,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ANGEL RAUL</t>
+          <t>IRENE BEATRIZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>02/10/1986</t>
+          <t>14/03/1991</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>47618809</t>
+          <t>73666024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IRENE BEATRIZ</t>
+          <t>RICHARD HUGO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14/03/1991</t>
+          <t>12/05/1994</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>73666024</t>
+          <t>73666023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RICHARD HUGO</t>
+          <t>GILVER MIGUEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12/05/1994</t>
+          <t>04/09/1998</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>27/01/2015</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>73666023</t>
+          <t>20968672</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GILVER MIGUEL</t>
+          <t>RAFAEL ARCANGEL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2778,16 +2778,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>04/09/1998</t>
+          <t>23/10/1957</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>27/01/2015</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20968672</t>
+          <t>20968788</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RAFAEL ARCANGEL</t>
+          <t>ANTOLINO ANTONIO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,11 +2841,11 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23/10/1957</t>
+          <t>17/10/1964</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20968788</t>
+          <t>20992890</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2895,25 +2895,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ANTOLINO ANTONIO</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17/10/1964</t>
+          <t>01/12/1969</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20992890</t>
+          <t>20997952</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2958,20 +2958,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>ADENCIO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01/12/1969</t>
+          <t>01/03/1972</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3006,7 +3006,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20997952</t>
+          <t>20998248</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3021,20 +3021,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ADENCIO</t>
+          <t>FRANCISCA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01/03/1972</t>
+          <t>09/03/1978</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3069,22 +3069,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20998248</t>
+          <t>60438518</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FRANCISCA</t>
+          <t>DEYSI AYDEE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>09/03/1978</t>
+          <t>01/10/2006</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>60438518</t>
+          <t>77124938</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3142,25 +3142,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>VILLANERA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DEYSI AYDEE</t>
+          <t>WILLY SMITH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01/10/2006</t>
+          <t>04/09/1998</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>04/12/2019</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,45 +3195,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>77124938</t>
+          <t>20968114</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VILLANERA</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>WILLY SMITH</t>
+          <t>MANUELA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>04/09/1998</t>
+          <t>08/12/1965</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>04/12/2019</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20968114</t>
+          <t>92137082</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GUERREROS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>LAVADO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MANUELA</t>
+          <t>ABRIL ARIEL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>08/12/1965</t>
+          <t>20/11/2020</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>06/04/2021</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,45 +3321,45 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>92137082</t>
+          <t>44278214</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUERREROS</t>
+          <t>GUTARRA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LAVADO</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ABRIL ARIEL</t>
+          <t>DAVID MANUEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20/11/2020</t>
+          <t>20/05/1987</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,45 +3384,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>44278214</t>
+          <t>81526380</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUTARRA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DAVID MANUEL</t>
+          <t>BRICEIDA MEDALID</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20/05/1987</t>
+          <t>04/07/2017</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>81526380</t>
+          <t>62291348</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BRICEIDA MEDALID</t>
+          <t>EMELY DEYSI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,16 +3471,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>04/07/2017</t>
+          <t>18/05/2011</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>62291348</t>
+          <t>73392160</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3520,30 +3520,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EMELY DEYSI</t>
+          <t>HERMENEGILDO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/05/2011</t>
+          <t>02/02/1994</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>73392160</t>
+          <t>73660249</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HERMENEGILDO</t>
+          <t>FRANKLIN DANIEL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>02/02/1994</t>
+          <t>30/04/2003</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>73660249</t>
+          <t>73660248</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3651,20 +3651,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FRANKLIN DANIEL</t>
+          <t>DAYCE ROSALINDA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>30/04/2003</t>
+          <t>11/05/2004</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>73660248</t>
+          <t>73660238</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DAYCE ROSALINDA</t>
+          <t>JOEL ELISEO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11/05/2004</t>
+          <t>16/11/2004</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>73660238</t>
+          <t>61567974</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,20 +3777,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JOEL ELISEO</t>
+          <t>RAQUEL NOEMI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>16/11/2004</t>
+          <t>25/09/2008</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>25/01/2019</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>61567974</t>
+          <t>81411686</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,25 +3840,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RAQUEL NOEMI</t>
+          <t>SAMUEL CALEB</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25/09/2008</t>
+          <t>25/09/2014</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>25/01/2019</t>
+          <t>06/07/2015</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>81411686</t>
+          <t>20997990</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3898,30 +3898,30 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>NAULA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAMUEL CALEB</t>
+          <t>MARIA HORTENCIA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>25/09/2014</t>
+          <t>10/04/1962</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>06/07/2015</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20997990</t>
+          <t>20998168</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3966,20 +3966,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MARIA HORTENCIA</t>
+          <t>EFRAIN PAULINO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10/04/1962</t>
+          <t>18/08/1965</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20998168</t>
+          <t>20997989</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EFRAIN PAULINO</t>
+          <t>UBALDO ARMANDO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>18/08/1965</t>
+          <t>23/09/1972</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20997989</t>
+          <t>48894782</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4092,20 +4092,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UBALDO ARMANDO</t>
+          <t>REBECA NORMA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>23/09/1972</t>
+          <t>06/03/1975</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>07/10/2015</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,7 +4140,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>48894782</t>
+          <t>41080188</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4155,20 +4155,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>REBECA NORMA</t>
+          <t>EVER ROLANDO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>06/03/1975</t>
+          <t>19/04/1978</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>07/10/2015</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>41080188</t>
+          <t>75323517</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NAULA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EVER ROLANDO</t>
+          <t>EVER CLAUDIO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19/04/1978</t>
+          <t>26/04/1996</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>75323517</t>
+          <t>81411651</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EVER CLAUDIO</t>
+          <t>ALDAHIR SNAHIDER</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>26/04/1996</t>
+          <t>08/05/2014</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>81411651</t>
+          <t>48178963</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4339,35 +4339,35 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ALDAHIR SNAHIDER</t>
+          <t>CARMEN VIRGINIA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>08/05/2014</t>
+          <t>04/09/1989</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>06/08/2012</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,35 +4392,35 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>48178963</t>
+          <t>43503904</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CARMEN VIRGINIA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>04/09/1989</t>
+          <t>17/06/1983</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>06/08/2012</t>
+          <t>25/01/2019</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>43503904</t>
+          <t>77796637</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4479,16 +4479,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17/06/1983</t>
+          <t>18/12/1999</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>25/01/2019</t>
+          <t>17/09/2020</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>77796637</t>
+          <t>73666028</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>JUAN LUIS RICARDO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,11 +4542,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/12/1999</t>
+          <t>21/01/1998</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17/09/2020</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,35 +4581,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>73666028</t>
+          <t>78109188</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>LAVADO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>JUAN LUIS RICARDO</t>
+          <t>NILDA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21/01/1998</t>
+          <t>10/05/2004</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>78109188</t>
+          <t>60366708</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NILDA</t>
+          <t>ESVILDA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,11 +4668,11 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10/05/2004</t>
+          <t>21/06/2008</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>30/04/2013</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>60366708</t>
+          <t>63358103</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ESVILDA</t>
+          <t>YERSILA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21/06/2008</t>
+          <t>16/07/2011</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4770,7 +4770,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>63358103</t>
+          <t>81526313</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4785,25 +4785,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>YERSILA</t>
+          <t>KENEL LUIAN</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>16/07/2011</t>
+          <t>24/05/2016</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>30/04/2013</t>
+          <t>07/03/2017</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>81526313</t>
+          <t>20993892</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>SIGUIL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KENEL LUIAN</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>24/05/2016</t>
+          <t>25/08/1967</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>07/03/2017</t>
+          <t>30/04/2013</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20993892</t>
+          <t>78303226</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LAVADO</t>
+          <t>LEANDRO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SIGUIL</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>DANIEL ALEJANDRO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>25/08/1967</t>
+          <t>26/09/2013</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>30/04/2013</t>
+          <t>17/03/2016</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,22 +4959,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>78303226</t>
+          <t>75338604</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>LLANTO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DANIEL ALEJANDRO</t>
+          <t>FRANK JULINO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>26/09/2013</t>
+          <t>24/01/1997</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17/03/2016</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,22 +5022,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>75338604</t>
+          <t>20404365</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LLANTO</t>
+          <t>MAMANI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>Y AVELLANEDA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FRANK JULINO</t>
+          <t>JESUS PASCUAL</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5046,21 +5046,21 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>24/01/1997</t>
+          <t>25/12/1954</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>31/05/2017</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,169 +5085,169 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20404365</t>
+          <t>60010731</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MAMANI</t>
+          <t>MARAVI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Y AVELLANEDA</t>
+          <t>VALTOP</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>JESUS PASCUAL</t>
+          <t>ADRIANA LEZLY</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>20</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>17/07/2006</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MARINGAMA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>GODOY</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>KILIAN AKE</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>72</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>25/12/1954</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>5.ADULTO MAYOR</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>31/05/2017</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>60010731</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MARAVI</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>VALTOP</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>ADRIANA LEZLY</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17/07/2006</t>
+          <t>08/09/2023</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>08/09/2023</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>74254927</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MAYTA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>JOSE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>KLINTON JITLER</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>31</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>25/02/1995</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
           <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>06/01/2025</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MARINGAMA</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>GODOY</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>KILIAN AKE</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>08/09/2023</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>08/09/2023</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5270,45 +5270,45 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>74254927</t>
+          <t>62173929</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KLINTON JITLER</t>
+          <t>KATERIN VICKY</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>25/02/1995</t>
+          <t>17/07/2002</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>15/03/2012</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>62173929</t>
+          <t>61697332</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KATERIN VICKY</t>
+          <t>MARYCHUY MARDELY</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5357,16 +5357,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>17/07/2002</t>
+          <t>15/04/2010</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>15/03/2012</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5396,7 +5396,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>61697332</t>
+          <t>80846582</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5411,20 +5411,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MARYCHUY MARDELY</t>
+          <t>JHOMAR FERNANDO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>15/04/2010</t>
+          <t>17/07/2013</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>09/02/2015</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>80846582</t>
+          <t>41734435</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>INOCENTE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JHOMAR FERNANDO</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5483,16 +5483,16 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>17/07/2013</t>
+          <t>26/02/1982</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>09/02/2015</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5522,35 +5522,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41734435</t>
+          <t>77424569</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>INOCENTE</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>KARINA SOFIA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>26/02/1982</t>
+          <t>04/03/1995</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>08/07/2013</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5585,22 +5585,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>77424569</t>
+          <t>76058938</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KARINA SOFIA</t>
+          <t>MISHEEL STEFANY</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5609,21 +5609,21 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>04/03/1995</t>
+          <t>29/09/2001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>08/07/2013</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>76058938</t>
+          <t>81479861</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5658,30 +5658,30 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MISHEEL STEFANY</t>
+          <t>KARIM GARETH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>29/09/2001</t>
+          <t>28/10/2015</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5711,22 +5711,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>81479861</t>
+          <t>31177278</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>OSCCO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KARIM GARETH</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>28/10/2015</t>
+          <t>23/09/1971</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>05/07/2012</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5774,7 +5774,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>31177278</t>
+          <t>73664452</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5784,35 +5784,35 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OSCCO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>NELY SONIA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23/09/1971</t>
+          <t>24/06/2005</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>05/07/2012</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5837,7 +5837,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>73664452</t>
+          <t>60203478</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5852,20 +5852,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NELY SONIA</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>24/06/2005</t>
+          <t>01/12/2006</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5900,22 +5900,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>60203478</t>
+          <t>61697277</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>01/12/2006</t>
+          <t>23/08/2009</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5963,22 +5963,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>61697277</t>
+          <t>94524162</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>PALACIN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>PATRICK CASH</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23/08/2009</t>
+          <t>24/01/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6026,22 +6026,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>94524162</t>
+          <t>80846596</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PALACIN</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PATRICK CASH</t>
+          <t>DAVID JUAN</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>24/01/2026</t>
+          <t>20/10/2012</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>05/07/2015</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6089,22 +6089,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>80846596</t>
+          <t>44666769</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>CANCHUMUNI</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DAVID JUAN</t>
+          <t>JOEL EMERSON</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6113,21 +6113,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20/10/2012</t>
+          <t>18/09/1987</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>05/07/2015</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6152,22 +6152,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>44666769</t>
+          <t>77350391</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CANCHUMUNI</t>
+          <t>CANCHOMONI</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>JOEL EMERSON</t>
+          <t>RONALD EDWIN</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/09/1987</t>
+          <t>25/05/1995</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>19/09/2013</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6215,7 +6215,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>77350391</t>
+          <t>40867709</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6225,25 +6225,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CANCHOMONI</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>RONALD EDWIN</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>25/05/1995</t>
+          <t>20/12/1979</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>19/09/2013</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6278,7 +6278,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>40867709</t>
+          <t>78522035</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6288,35 +6288,35 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>THIAGO PATRIX</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20/12/1979</t>
+          <t>23/03/2014</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>16/05/2014</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6341,22 +6341,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>78522035</t>
+          <t>47350538</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>THIAGO PATRIX</t>
+          <t>ALFONSO</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>23/03/2014</t>
+          <t>29/07/1992</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>16/05/2014</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6404,22 +6404,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>47350538</t>
+          <t>72944824</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>POMAYLLA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ALFONSO</t>
+          <t>JEAN CARLOS</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6428,11 +6428,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>29/07/1992</t>
+          <t>10/08/1993</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>08/07/2013</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6467,22 +6467,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>72944824</t>
+          <t>60203490</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>POMAYLLA</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>JEAN CARLOS</t>
+          <t>ALEXIS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6491,21 +6491,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>10/08/1993</t>
+          <t>28/11/2006</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>08/07/2013</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6530,12 +6530,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>60203490</t>
+          <t>73667970</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>QUICHCA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6545,20 +6545,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ALEXIS</t>
+          <t>MAYLIT RITA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>28/11/2006</t>
+          <t>27/11/2000</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>12/04/2017</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6593,7 +6593,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>73667970</t>
+          <t>61567999</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>MAYLIT RITA</t>
+          <t>JHAKELYN KELY</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>27/11/2000</t>
+          <t>02/12/2008</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>12/04/2017</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>61567999</t>
+          <t>90592913</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>JHAKELYN KELY</t>
+          <t>RUTH JANDY</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6680,21 +6680,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>02/12/2008</t>
+          <t>06/01/2018</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>06/01/2023</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6719,7 +6719,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>90592913</t>
+          <t>93933866</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RUTH JANDY</t>
+          <t>ANAHI TABITA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6743,11 +6743,11 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>06/01/2018</t>
+          <t>09/08/2024</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>06/01/2023</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>93933866</t>
+          <t>93018637</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6792,25 +6792,25 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ANAHI TABITA</t>
+          <t>JOSUE ABDIEL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>09/08/2024</t>
+          <t>14/08/2022</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6845,45 +6845,45 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>93018637</t>
+          <t>60248610</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>QUICHCA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>JOSUE ABDIEL</t>
+          <t>SAYDI YURI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>14/08/2022</t>
+          <t>27/03/2007</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6908,7 +6908,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>60248610</t>
+          <t>74276226</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6918,25 +6918,25 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAYDI YURI</t>
+          <t>JUAN ELIAS</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>27/03/2007</t>
+          <t>19/01/2001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6971,40 +6971,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>74276226</t>
+          <t>20968504</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DE CORDOVA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JUAN ELIAS</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>19/01/2001</t>
+          <t>20/10/1960</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7034,17 +7034,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20968504</t>
+          <t>20968563</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DE CORDOVA</t>
+          <t>BACA DE DE LA O</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20/10/1960</t>
+          <t>20/10/1944</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>21/11/2012</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7097,22 +7097,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20968563</t>
+          <t>31184110</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BACA DE DE LA O</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7121,16 +7121,16 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20/10/1944</t>
+          <t>25/07/1976</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>21/11/2012</t>
+          <t>21/06/2023</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7160,7 +7160,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>31184110</t>
+          <t>78907962</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7170,35 +7170,35 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>GARETH BALE MARK</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>25/07/1976</t>
+          <t>07/12/2014</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>21/06/2023</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7223,22 +7223,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>78907962</t>
+          <t>73447050</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>GARETH BALE MARK</t>
+          <t>EDGAR EDUARDO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7247,16 +7247,16 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>07/12/2014</t>
+          <t>25/05/1993</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>18/04/2024</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7286,22 +7286,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>73447050</t>
+          <t>60434248</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CHUJUTALLI</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EDGAR EDUARDO</t>
+          <t>CHAN SUNYO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7310,16 +7310,16 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>25/05/1993</t>
+          <t>13/12/2006</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7349,22 +7349,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>60434248</t>
+          <t>61739792</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CHUJUTALLI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CHAN SUNYO</t>
+          <t>JEANPIER DIEGO</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>13/12/2006</t>
+          <t>16/09/2009</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>09/03/2015</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7412,22 +7412,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>61240357</t>
+          <t>81479831</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HUAMANCHAQUI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TERRY JHON</t>
+          <t>CRISTIAM ALEXIS</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7436,16 +7436,16 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>25/06/2005</t>
+          <t>10/06/2015</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>61739792</t>
+          <t>45854743</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HUANCAS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>JEANPIER DIEGO</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7499,16 +7499,16 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>16/09/2009</t>
+          <t>02/01/1978</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>09/03/2015</t>
+          <t>10/04/2018</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7538,22 +7538,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>81479831</t>
+          <t>46891699</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SOBRADO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>MARCHINO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CRISTIAM ALEXIS</t>
+          <t>AHOLIAB ZACARIAS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7562,16 +7562,16 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10/06/2015</t>
+          <t>02/11/1990</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7601,22 +7601,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>45854743</t>
+          <t>20997966</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HUANCAS</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>WALTER EDMUNDO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7625,16 +7625,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>02/01/1978</t>
+          <t>09/11/1966</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>10/04/2018</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7664,45 +7664,45 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>46891699</t>
+          <t>81391391</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SOBRADO</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MARCHINO</t>
+          <t>CAVIÑO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AHOLIAB ZACARIAS</t>
+          <t>AKEMY DAYZUQUI</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>02/11/1990</t>
+          <t>04/01/2002</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7727,40 +7727,40 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20997966</t>
+          <t>77242280</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>POVIS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>WALTER EDMUNDO</t>
+          <t>ERIKA MARLENI</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>09/11/1966</t>
+          <t>17/02/1995</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>19/09/2013</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7790,22 +7790,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>81391391</t>
+          <t>61282617</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CAVIÑO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AKEMY DAYZUQUI</t>
+          <t>YIN SUE SHIRLEY</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7814,11 +7814,11 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>04/01/2002</t>
+          <t>04/02/2008</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7853,22 +7853,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>77242280</t>
+          <t>20968626</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>POVIS</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ERIKA MARLENI</t>
+          <t>REGINA LUISA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7877,21 +7877,21 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>17/02/1995</t>
+          <t>07/09/1957</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>19/09/2013</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7916,40 +7916,40 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>61282617</t>
+          <t>42978891</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>URETA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>YIN SUE SHIRLEY</t>
+          <t>ROY MIRKO</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>04/02/2008</t>
+          <t>10/10/1984</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7979,22 +7979,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>41223863</t>
+          <t>81411696</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>COOPER PERCY</t>
+          <t>JHONN ALEXIS</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8003,16 +8003,16 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>19/02/1982</t>
+          <t>15/11/2014</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8042,22 +8042,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20968626</t>
+          <t>73668035</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VILCHEZ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>MUNIVE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>REGINA LUISA</t>
+          <t>LUCY JHANET</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8066,16 +8066,16 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>07/09/1957</t>
+          <t>21/03/1998</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8099,195 +8099,6 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>42978891</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>URETA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>CAMPOS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ROY MIRKO</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>42</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>10/10/1984</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>06/03/2024</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M123" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>81411696</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>VELIZ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>HINOSTROZA</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>JHONN ALEXIS</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>12</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>15/11/2014</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>2.ADOLESCENTE</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>15/05/2025</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M124" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>73668035</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>VILCHEZ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>MUNIVE</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LUCY JHANET</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>28</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>21/03/1998</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>05/04/2025</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
         <v>120602</v>
       </c>
     </row>

--- a/exports/7186_palmapampa.xlsx
+++ b/exports/7186_palmapampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,22 +486,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>63410575</t>
+          <t>71118126</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANCCO</t>
+          <t>AMPICHA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>MACHARI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MATHIAS FERNANDO</t>
+          <t>EFRAIN ELFREN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -510,21 +510,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30/09/2011</t>
+          <t>27/11/1994</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -549,22 +549,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>43108917</t>
+          <t>63410575</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARANGOITIA</t>
+          <t>ANCCO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GYNO PAUL</t>
+          <t>MATHIAS FERNANDO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20/10/1979</t>
+          <t>30/09/2011</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -612,22 +612,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>42849494</t>
+          <t>43108917</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BALBIN</t>
+          <t>ARANGOITIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LEOPOLDO DANTE</t>
+          <t>GYNO PAUL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -636,11 +636,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06/11/1984</t>
+          <t>20/10/1979</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18/04/2024</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -675,35 +675,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>45766609</t>
+          <t>42849494</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>BALBIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RUTH EGLIA</t>
+          <t>LEOPOLDO DANTE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/05/1989</t>
+          <t>06/11/1984</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -738,22 +738,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>73362844</t>
+          <t>45766609</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BARJA</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VIVANCO</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>YISENIA ERIKA</t>
+          <t>RUTH EGLIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22/12/1992</t>
+          <t>27/05/1989</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>05/01/2016</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -801,22 +801,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>60438604</t>
+          <t>73362844</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BARRIENTOS</t>
+          <t>BARJA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CASALLO</t>
+          <t>VIVANCO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CLAUDIA PATRICIA</t>
+          <t>YISENIA ERIKA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -825,21 +825,21 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>04/11/2006</t>
+          <t>22/12/1992</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>05/01/2016</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -864,22 +864,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>73119874</t>
+          <t>60438604</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BENAVIDES</t>
+          <t>BARRIENTOS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CASALLO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MEREDITH GIANINA</t>
+          <t>CLAUDIA PATRICIA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18/06/1994</t>
+          <t>04/11/2006</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -927,22 +927,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>91024306</t>
+          <t>73119874</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>BENAVIDES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>YOSELI MILENA</t>
+          <t>MEREDITH GIANINA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26/10/2018</t>
+          <t>18/06/1994</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26/10/2023</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -990,40 +990,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20977431</t>
+          <t>91024306</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLANCAS</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MAXIMO</t>
+          <t>YOSELI MILENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14/01/1946</t>
+          <t>26/10/2018</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>26/10/2023</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>41376993</t>
+          <t>20977431</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,30 +1063,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>BLANCAS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SONIA LEONCIA</t>
+          <t>MAXIMO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01/08/1982</t>
+          <t>14/01/1946</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1116,22 +1116,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>41458267</t>
+          <t>41376993</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EVA TOMAZA</t>
+          <t>SONIA LEONCIA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20/07/1982</t>
+          <t>01/08/1982</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1179,40 +1179,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20997828</t>
+          <t>41458267</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CANCHUMONI</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>EVA TOMAZA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14/03/1955</t>
+          <t>20/07/1982</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14/10/2013</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1242,45 +1242,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>48415035</t>
+          <t>20997828</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>CANCHUMONI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TEOFILA VICTORIA</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13/02/1991</t>
+          <t>14/03/1955</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>14/10/2013</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>48829771</t>
+          <t>48415035</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>YAQUELINA ROCIO</t>
+          <t>TEOFILA VICTORIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1329,11 +1329,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>03/11/1989</t>
+          <t>13/02/1991</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>09/09/2015</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>93056956</t>
+          <t>48829771</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AZUMI ADELAIDA</t>
+          <t>YAQUELINA ROCIO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1392,21 +1392,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12/09/2022</t>
+          <t>03/11/1989</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>03/01/2023</t>
+          <t>09/09/2015</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,22 +1431,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>73389175</t>
+          <t>93056956</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CARRASCO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RUTH</t>
+          <t>AZUMI ADELAIDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01/05/1994</t>
+          <t>12/09/2022</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>03/01/2023</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,22 +1494,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>48829389</t>
+          <t>73389175</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>CARRASCO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JACINTA</t>
+          <t>RUTH</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1518,11 +1518,11 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/08/1970</t>
+          <t>01/05/1994</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>26/05/2015</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1557,22 +1557,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20997773</t>
+          <t>91765942</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>CAVERO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MAXIMO ALEJANDRO</t>
+          <t>PAUL AMETH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29/05/1971</t>
+          <t>09/03/2020</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,40 +1620,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>73664428</t>
+          <t>48829389</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EDWIN</t>
+          <t>JACINTA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16/03/2002</t>
+          <t>06/08/1970</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>26/05/2015</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2124,22 +2124,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>90660467</t>
+          <t>79329682</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ECHEVARRIA</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>QUICHCA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ABEL YEICO</t>
+          <t>KALED ANDRE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2148,11 +2148,11 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>03/03/2018</t>
+          <t>23/09/2015</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,40 +2187,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>60010710</t>
+          <t>90660467</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>ECHEVARRIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>QUICHCA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NATALY YESENIA</t>
+          <t>ABEL YEICO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>02/12/1996</t>
+          <t>03/03/2018</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,22 +2250,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>73664445</t>
+          <t>60010710</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LISBETH GUISELA</t>
+          <t>NATALY YESENIA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,11 +2274,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>08/07/1999</t>
+          <t>02/12/1996</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>73660242</t>
+          <t>73664445</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LUZMILA SHEILA</t>
+          <t>LISBETH GUISELA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13/11/2000</t>
+          <t>08/07/1999</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2376,7 +2376,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>63410555</t>
+          <t>73660242</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LUZ MELIZA</t>
+          <t>LUZMILA SHEILA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>05/07/2011</t>
+          <t>13/11/2000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>05/12/2011</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>90688461</t>
+          <t>63410555</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2454,25 +2454,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JESUS YODIEL</t>
+          <t>LUZ MELIZA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21/03/2018</t>
+          <t>05/07/2011</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21/03/2023</t>
+          <t>05/12/2011</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43847576</t>
+          <t>90688461</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ANGEL RAUL</t>
+          <t>JESUS YODIEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2526,16 +2526,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02/10/1986</t>
+          <t>21/03/2018</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>21/03/2023</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>47618809</t>
+          <t>43847576</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2580,20 +2580,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IRENE BEATRIZ</t>
+          <t>ANGEL RAUL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14/03/1991</t>
+          <t>02/10/1986</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>73666024</t>
+          <t>47618809</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RICHARD HUGO</t>
+          <t>IRENE BEATRIZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12/05/1994</t>
+          <t>14/03/1991</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>73666023</t>
+          <t>73666024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GILVER MIGUEL</t>
+          <t>RICHARD HUGO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>04/09/1998</t>
+          <t>12/05/1994</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>27/01/2015</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20968672</t>
+          <t>73666023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RAFAEL ARCANGEL</t>
+          <t>GILVER MIGUEL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2778,16 +2778,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23/10/1957</t>
+          <t>04/09/1998</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>27/01/2015</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20968788</t>
+          <t>20968672</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ANTOLINO ANTONIO</t>
+          <t>RAFAEL ARCANGEL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,11 +2841,11 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17/10/1964</t>
+          <t>23/10/1957</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20992890</t>
+          <t>20968788</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2895,25 +2895,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>ANTOLINO ANTONIO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01/12/1969</t>
+          <t>17/10/1964</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20997952</t>
+          <t>20992890</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2958,20 +2958,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ADENCIO</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01/03/1972</t>
+          <t>01/12/1969</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3006,7 +3006,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20998248</t>
+          <t>20997952</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3021,20 +3021,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FRANCISCA</t>
+          <t>ADENCIO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>09/03/1978</t>
+          <t>01/03/1972</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3069,22 +3069,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>60438518</t>
+          <t>20998248</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DEYSI AYDEE</t>
+          <t>FRANCISCA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01/10/2006</t>
+          <t>09/03/1978</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>77124938</t>
+          <t>60438518</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3142,25 +3142,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VILLANERA</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WILLY SMITH</t>
+          <t>DEYSI AYDEE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>04/09/1998</t>
+          <t>01/10/2006</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>04/12/2019</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,45 +3195,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20968114</t>
+          <t>77124938</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>VILLANERA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MANUELA</t>
+          <t>WILLY SMITH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>08/12/1965</t>
+          <t>04/09/1998</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>04/12/2019</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>92137082</t>
+          <t>20968114</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GUERREROS</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LAVADO</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ABRIL ARIEL</t>
+          <t>MANUELA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20/11/2020</t>
+          <t>08/12/1965</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,45 +3321,45 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>44278214</t>
+          <t>92137082</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUTARRA</t>
+          <t>GUERREROS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>LAVADO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DAVID MANUEL</t>
+          <t>ABRIL ARIEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20/05/1987</t>
+          <t>20/11/2020</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>06/04/2021</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,45 +3384,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>81526380</t>
+          <t>44278214</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>GUTARRA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BRICEIDA MEDALID</t>
+          <t>DAVID MANUEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>04/07/2017</t>
+          <t>20/05/1987</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>62291348</t>
+          <t>81526380</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EMELY DEYSI</t>
+          <t>BRICEIDA MEDALID</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,16 +3471,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/05/2011</t>
+          <t>04/07/2017</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>73392160</t>
+          <t>62291348</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3520,30 +3520,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>HERMENEGILDO</t>
+          <t>EMELY DEYSI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>02/02/1994</t>
+          <t>18/05/2011</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>73660249</t>
+          <t>73392160</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FRANKLIN DANIEL</t>
+          <t>HERMENEGILDO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>30/04/2003</t>
+          <t>02/02/1994</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>73660248</t>
+          <t>73660249</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3651,20 +3651,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DAYCE ROSALINDA</t>
+          <t>FRANKLIN DANIEL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>11/05/2004</t>
+          <t>30/04/2003</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>73660238</t>
+          <t>73660248</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JOEL ELISEO</t>
+          <t>DAYCE ROSALINDA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16/11/2004</t>
+          <t>11/05/2004</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>61567974</t>
+          <t>73660238</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,20 +3777,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RAQUEL NOEMI</t>
+          <t>JOEL ELISEO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>25/09/2008</t>
+          <t>16/11/2004</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>25/01/2019</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>81411686</t>
+          <t>61567974</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,25 +3840,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAMUEL CALEB</t>
+          <t>RAQUEL NOEMI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25/09/2014</t>
+          <t>25/09/2008</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>06/07/2015</t>
+          <t>25/01/2019</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20997990</t>
+          <t>81411686</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3898,30 +3898,30 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NAULA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>MARIA HORTENCIA</t>
+          <t>SAMUEL CALEB</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>10/04/1962</t>
+          <t>25/09/2014</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>06/07/2015</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20998168</t>
+          <t>20997990</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3966,20 +3966,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EFRAIN PAULINO</t>
+          <t>MARIA HORTENCIA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/08/1965</t>
+          <t>10/04/1962</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20997989</t>
+          <t>20998168</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>UBALDO ARMANDO</t>
+          <t>EFRAIN PAULINO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>23/09/1972</t>
+          <t>18/08/1965</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>48894782</t>
+          <t>20997989</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4092,20 +4092,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>REBECA NORMA</t>
+          <t>UBALDO ARMANDO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>06/03/1975</t>
+          <t>23/09/1972</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>07/10/2015</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,7 +4140,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>41080188</t>
+          <t>48894782</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4155,20 +4155,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EVER ROLANDO</t>
+          <t>REBECA NORMA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19/04/1978</t>
+          <t>06/03/1975</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>07/10/2015</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>75323517</t>
+          <t>41080188</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>NAULA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EVER CLAUDIO</t>
+          <t>EVER ROLANDO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>26/04/1996</t>
+          <t>19/04/1978</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>81411651</t>
+          <t>75323517</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ALDAHIR SNAHIDER</t>
+          <t>EVER CLAUDIO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>08/05/2014</t>
+          <t>26/04/1996</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>48178963</t>
+          <t>81411651</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4339,35 +4339,35 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CARMEN VIRGINIA</t>
+          <t>ALDAHIR SNAHIDER</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>04/09/1989</t>
+          <t>08/05/2014</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>06/08/2012</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,35 +4392,35 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>43503904</t>
+          <t>48178963</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>CARMEN VIRGINIA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17/06/1983</t>
+          <t>04/09/1989</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>25/01/2019</t>
+          <t>06/08/2012</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>77796637</t>
+          <t>43503904</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4479,16 +4479,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18/12/1999</t>
+          <t>17/06/1983</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17/09/2020</t>
+          <t>25/01/2019</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>73666028</t>
+          <t>77796637</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JUAN LUIS RICARDO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,11 +4542,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21/01/1998</t>
+          <t>18/12/1999</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>17/09/2020</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,35 +4581,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>78109188</t>
+          <t>73666028</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LAVADO</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NILDA</t>
+          <t>JUAN LUIS RICARDO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10/05/2004</t>
+          <t>21/01/1998</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>60366708</t>
+          <t>78109188</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ESVILDA</t>
+          <t>NILDA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,11 +4668,11 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21/06/2008</t>
+          <t>10/05/2004</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>30/04/2013</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>63358103</t>
+          <t>60366708</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>YERSILA</t>
+          <t>ESVILDA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>16/07/2011</t>
+          <t>21/06/2008</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4770,7 +4770,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>81526313</t>
+          <t>63358103</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4785,25 +4785,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KENEL LUIAN</t>
+          <t>YERSILA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>24/05/2016</t>
+          <t>16/07/2011</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>07/03/2017</t>
+          <t>30/04/2013</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20993892</t>
+          <t>81526313</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIGUIL</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>KENEL LUIAN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>25/08/1967</t>
+          <t>24/05/2016</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>30/04/2013</t>
+          <t>07/03/2017</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>78303226</t>
+          <t>20993892</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>LAVADO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>SIGUIL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DANIEL ALEJANDRO</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>26/09/2013</t>
+          <t>25/08/1967</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17/03/2016</t>
+          <t>30/04/2013</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,22 +4959,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>75338604</t>
+          <t>78303226</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LLANTO</t>
+          <t>LEANDRO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FRANK JULINO</t>
+          <t>DANIEL ALEJANDRO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>24/01/1997</t>
+          <t>26/09/2013</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>17/03/2016</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,22 +5022,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20404365</t>
+          <t>75338604</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MAMANI</t>
+          <t>LLANTO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Y AVELLANEDA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>JESUS PASCUAL</t>
+          <t>FRANK JULINO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5046,21 +5046,21 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>25/12/1954</t>
+          <t>24/01/1997</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31/05/2017</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,177 +5085,177 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>20404365</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MAMANI</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Y AVELLANEDA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>JESUS PASCUAL</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>71</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>25/12/1954</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>31/05/2017</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>60010731</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>MARAVI</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>VALTOP</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>ADRIANA LEZLY</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="F76" t="n">
         <v>20</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>17/07/2006</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>3.JOVEN</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>06/01/2025</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
         <is>
           <t>MARINGAMA</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>GODOY</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>KILIAN AKE</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F76" t="n">
+      <c r="F77" t="n">
         <v>3</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>08/09/2023</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>08/09/2023</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>74254927</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MAYTA</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>JOSE</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>KLINTON JITLER</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>31</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>25/02/1995</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5270,40 +5270,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>62173929</t>
+          <t>74254927</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KATERIN VICKY</t>
+          <t>KLINTON JITLER</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/07/2002</t>
+          <t>25/02/1995</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>15/03/2012</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>61697332</t>
+          <t>62173929</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MARYCHUY MARDELY</t>
+          <t>KATERIN VICKY</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5357,16 +5357,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>15/04/2010</t>
+          <t>17/07/2002</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>15/03/2012</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5396,7 +5396,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>80846582</t>
+          <t>61697332</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5411,20 +5411,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JHOMAR FERNANDO</t>
+          <t>MARYCHUY MARDELY</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/07/2013</t>
+          <t>15/04/2010</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>09/02/2015</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41734435</t>
+          <t>80846582</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>INOCENTE</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>JHOMAR FERNANDO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5483,16 +5483,16 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>26/02/1982</t>
+          <t>17/07/2013</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>09/02/2015</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5522,35 +5522,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>77424569</t>
+          <t>41734435</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>INOCENTE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KARINA SOFIA</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>04/03/1995</t>
+          <t>26/02/1982</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>08/07/2013</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5585,22 +5585,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>76058938</t>
+          <t>77424569</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MISHEEL STEFANY</t>
+          <t>KARINA SOFIA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5609,21 +5609,21 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>29/09/2001</t>
+          <t>04/03/1995</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>08/07/2013</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>81479861</t>
+          <t>76058938</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5658,30 +5658,30 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KARIM GARETH</t>
+          <t>MISHEEL STEFANY</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>28/10/2015</t>
+          <t>29/09/2001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5711,22 +5711,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>31177278</t>
+          <t>81479861</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OSCCO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>KARIM GARETH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>23/09/1971</t>
+          <t>28/10/2015</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>05/07/2012</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5774,35 +5774,35 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>73664452</t>
+          <t>75550595</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>MARTEL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NELY SONIA</t>
+          <t>KELVIN</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>24/06/2005</t>
+          <t>21/11/2005</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5837,7 +5837,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>60203478</t>
+          <t>31177278</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>OSCCO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5861,21 +5861,21 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>01/12/2006</t>
+          <t>23/09/1971</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>05/07/2012</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5900,45 +5900,45 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>61697277</t>
+          <t>73664452</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>NELY SONIA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23/08/2009</t>
+          <t>24/06/2005</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5963,22 +5963,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>94524162</t>
+          <t>60203478</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PALACIN</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PATRICK CASH</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>24/01/2026</t>
+          <t>01/12/2006</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6026,22 +6026,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>80846596</t>
+          <t>61697277</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DAVID JUAN</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6050,11 +6050,11 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20/10/2012</t>
+          <t>23/08/2009</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>05/07/2015</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6089,22 +6089,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>44666769</t>
+          <t>94524162</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PALACIN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CANCHUMUNI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>JOEL EMERSON</t>
+          <t>PATRICK CASH</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6113,21 +6113,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/09/1987</t>
+          <t>24/01/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6152,22 +6152,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>77350391</t>
+          <t>80846596</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CANCHOMONI</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>RONALD EDWIN</t>
+          <t>DAVID JUAN</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6176,16 +6176,16 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>25/05/1995</t>
+          <t>20/10/2012</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>19/09/2013</t>
+          <t>05/07/2015</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6215,35 +6215,35 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>40867709</t>
+          <t>44666769</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>CANCHUMUNI</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>JOEL EMERSON</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20/12/1979</t>
+          <t>18/09/1987</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6278,7 +6278,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>78522035</t>
+          <t>77350391</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>CANCHOMONI</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>THIAGO PATRIX</t>
+          <t>RONALD EDWIN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6302,16 +6302,16 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23/03/2014</t>
+          <t>25/05/1995</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>16/05/2014</t>
+          <t>19/09/2013</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6341,22 +6341,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>47350538</t>
+          <t>78522035</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ALFONSO</t>
+          <t>THIAGO PATRIX</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>29/07/1992</t>
+          <t>23/03/2014</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>16/05/2014</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6404,22 +6404,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>72944824</t>
+          <t>47350538</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>POMAYLLA</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>JEAN CARLOS</t>
+          <t>ALFONSO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6428,11 +6428,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>10/08/1993</t>
+          <t>29/07/1992</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>08/07/2013</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6467,22 +6467,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>60203490</t>
+          <t>72944824</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>POMAYLLA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ALEXIS</t>
+          <t>JEAN CARLOS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6491,21 +6491,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>28/11/2006</t>
+          <t>10/08/1993</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>08/07/2013</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6530,12 +6530,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>73667970</t>
+          <t>60203490</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>QUICHCA</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6545,20 +6545,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MAYLIT RITA</t>
+          <t>ALEXIS</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>27/11/2000</t>
+          <t>28/11/2006</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>12/04/2017</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6593,7 +6593,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>61567999</t>
+          <t>73667970</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>JHAKELYN KELY</t>
+          <t>MAYLIT RITA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>02/12/2008</t>
+          <t>27/11/2000</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>12/04/2017</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>90592913</t>
+          <t>61567999</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RUTH JANDY</t>
+          <t>JHAKELYN KELY</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6680,21 +6680,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>06/01/2018</t>
+          <t>02/12/2008</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>06/01/2023</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6719,7 +6719,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>93933866</t>
+          <t>90592913</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ANAHI TABITA</t>
+          <t>RUTH JANDY</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6743,11 +6743,11 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>09/08/2024</t>
+          <t>06/01/2018</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>06/01/2023</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>93018637</t>
+          <t>93933866</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6792,25 +6792,25 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>JOSUE ABDIEL</t>
+          <t>ANAHI TABITA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>14/08/2022</t>
+          <t>09/08/2024</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6845,45 +6845,45 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>60248610</t>
+          <t>93018637</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUICHCA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SAYDI YURI</t>
+          <t>JOSUE ABDIEL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>27/03/2007</t>
+          <t>14/08/2022</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6908,7 +6908,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>74276226</t>
+          <t>60248610</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6918,25 +6918,25 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>JUAN ELIAS</t>
+          <t>SAYDI YURI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>19/01/2001</t>
+          <t>27/03/2007</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6971,40 +6971,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>20968504</t>
+          <t>74276226</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DE CORDOVA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>JUAN ELIAS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20/10/1960</t>
+          <t>19/01/2001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>17/12/2018</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7034,17 +7034,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20968563</t>
+          <t>20968504</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BACA DE DE LA O</t>
+          <t>DE CORDOVA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20/10/1944</t>
+          <t>20/10/1960</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>21/11/2012</t>
+          <t>17/12/2018</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7097,22 +7097,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31184110</t>
+          <t>20968563</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>BACA DE DE LA O</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7121,16 +7121,16 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>25/07/1976</t>
+          <t>20/10/1944</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>21/06/2023</t>
+          <t>21/11/2012</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7160,7 +7160,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>78907962</t>
+          <t>31184110</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7170,35 +7170,35 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>GARETH BALE MARK</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>07/12/2014</t>
+          <t>25/07/1976</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>18/04/2024</t>
+          <t>21/06/2023</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7223,22 +7223,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>73447050</t>
+          <t>78907962</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>EDGAR EDUARDO</t>
+          <t>GARETH BALE MARK</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7247,16 +7247,16 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>25/05/1993</t>
+          <t>07/12/2014</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7286,22 +7286,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>60434248</t>
+          <t>73447050</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CHUJUTALLI</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CHAN SUNYO</t>
+          <t>EDGAR EDUARDO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7310,16 +7310,16 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>13/12/2006</t>
+          <t>25/05/1993</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7349,22 +7349,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>61739792</t>
+          <t>60434248</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CHUJUTALLI</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>JEANPIER DIEGO</t>
+          <t>CHAN SUNYO</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7373,16 +7373,16 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>16/09/2009</t>
+          <t>13/12/2006</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>09/03/2015</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7412,7 +7412,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>81479831</t>
+          <t>61739792</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CRISTIAM ALEXIS</t>
+          <t>JEANPIER DIEGO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7436,21 +7436,21 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>10/06/2015</t>
+          <t>16/09/2009</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>09/03/2015</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>45854743</t>
+          <t>81479831</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HUANCAS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>CRISTIAM ALEXIS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7499,21 +7499,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>02/01/1978</t>
+          <t>10/06/2015</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>10/04/2018</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7538,22 +7538,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>46891699</t>
+          <t>45854743</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SOBRADO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MARCHINO</t>
+          <t>HUANCAS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AHOLIAB ZACARIAS</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7562,11 +7562,11 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>02/11/1990</t>
+          <t>02/01/1978</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>10/04/2018</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7601,22 +7601,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>20997966</t>
+          <t>46891699</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SOBRADO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>MARCHINO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>WALTER EDMUNDO</t>
+          <t>AHOLIAB ZACARIAS</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>09/11/1966</t>
+          <t>02/11/1990</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7664,40 +7664,40 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>81391391</t>
+          <t>20997966</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CAVIÑO</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AKEMY DAYZUQUI</t>
+          <t>WALTER EDMUNDO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>04/01/2002</t>
+          <t>09/11/1966</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7727,22 +7727,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>77242280</t>
+          <t>81391391</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>POVIS</t>
+          <t>CAVIÑO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ERIKA MARLENI</t>
+          <t>AKEMY DAYZUQUI</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7751,16 +7751,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>17/02/1995</t>
+          <t>04/01/2002</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>19/09/2013</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7790,22 +7790,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>61282617</t>
+          <t>77242280</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>POVIS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>YIN SUE SHIRLEY</t>
+          <t>ERIKA MARLENI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>04/02/2008</t>
+          <t>17/02/1995</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/09/2013</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7853,7 +7853,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>20968626</t>
+          <t>61282617</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>REGINA LUISA</t>
+          <t>YIN SUE SHIRLEY</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7877,16 +7877,16 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>07/09/1957</t>
+          <t>04/02/2008</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7916,40 +7916,40 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>42978891</t>
+          <t>20968626</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>URETA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ROY MIRKO</t>
+          <t>REGINA LUISA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>10/10/1984</t>
+          <t>07/09/1957</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7979,22 +7979,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>81411696</t>
+          <t>42978891</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>URETA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>JHONN ALEXIS</t>
+          <t>ROY MIRKO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8003,16 +8003,16 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>15/11/2014</t>
+          <t>10/10/1984</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8042,63 +8042,126 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>81411696</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>VELIZ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>HINOSTROZA</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>JHONN ALEXIS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>11</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>15/11/2014</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>15/05/2025</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t>73668035</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>VILCHEZ</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>MUNIVE</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>LUCY JHANET</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F122" t="n">
+      <c r="F123" t="n">
         <v>28</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>21/03/1998</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>3.JOVEN</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>05/04/2025</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M122" t="n">
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
         <v>120602</v>
       </c>
     </row>
